--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484126_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484126_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>B. PAÑART POSTIGO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8448</v>
+        <v>2.8772</v>
       </c>
       <c r="E2" t="n">
-        <v>1.454</v>
+        <v>2.1952</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3908</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5879</v>
+        <v>3.3299</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6382</v>
+        <v>2.489</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9497</v>
+        <v>0.8408</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1982</v>
+        <v>2.9943</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0777</v>
+        <v>2.9892</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1205</v>
+        <v>0.0051</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3897</v>
+        <v>0.3355</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4395</v>
+        <v>-0.5002</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8292</v>
+        <v>0.8357</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0696</v>
+        <v>-0.8064</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1813</v>
+        <v>0.1928</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8883</v>
+        <v>-0.9992</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9136</v>
+        <v>-0.4398</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5007</v>
+        <v>-0.4398</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. PAÑART POSTIGO</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6287</v>
+        <v>2.8332</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0308</v>
+        <v>1.4144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5978</v>
+        <v>1.4188</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3299</v>
+        <v>2.5879</v>
       </c>
       <c r="H3" t="n">
-        <v>2.489</v>
+        <v>1.6382</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8408</v>
+        <v>0.9497</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9943</v>
+        <v>2.1982</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9892</v>
+        <v>2.0777</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0051</v>
+        <v>0.1205</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3355</v>
+        <v>0.3897</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5002</v>
+        <v>-0.4395</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8357</v>
+        <v>0.8292</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7935</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0549</v>
+        <v>-1.0812</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0284</v>
+        <v>-0.221</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0833</v>
+        <v>-0.8603</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.4398</v>
+        <v>2.9136</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.4129</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4398</v>
+        <v>0.5007</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9177</v>
+        <v>2.2325</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3813</v>
+        <v>1.4436</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5364</v>
+        <v>0.7889</v>
       </c>
       <c r="G4" t="n">
         <v>3.3978</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6479</v>
+        <v>-0.3331</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0452</v>
+        <v>0.0171</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6027</v>
+        <v>-0.3502</v>
       </c>
       <c r="V4" t="n">
         <v>0.3581</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2283</v>
+        <v>0.8899</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2162</v>
+        <v>-0.114</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0121</v>
+        <v>1.0039</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3429</v>
+        <v>1.0067</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5191</v>
+        <v>0.8616</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1762</v>
+        <v>0.1451</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6199</v>
+        <v>0.7135</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.66</v>
+        <v>1.3911</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>-0.6776</v>
       </c>
       <c r="M5" t="n">
-        <v>0.277</v>
+        <v>0.2932</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1409</v>
+        <v>-0.5295</v>
       </c>
       <c r="O5" t="n">
-        <v>0.136</v>
+        <v>0.8227</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3729</v>
+        <v>0.0184</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5701</v>
+        <v>0.1644</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1973</v>
+        <v>-0.146</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
       <c r="W5" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>J. ROYO SANTOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6073</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3181</v>
+        <v>-0.6185</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9759</v>
+        <v>1.2258</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0067</v>
+        <v>0.7929</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8616</v>
+        <v>-0.0505</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1451</v>
+        <v>0.8434</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7135</v>
+        <v>0.6455</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3911</v>
+        <v>0.0806</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6776</v>
+        <v>0.5648</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2932</v>
+        <v>0.1474</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5295</v>
+        <v>-0.1312</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8227</v>
+        <v>0.2786</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3968</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2137</v>
+        <v>0.2111</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0396</v>
+        <v>-0.272</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1741</v>
+        <v>0.4832</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROYO SANTOS</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.527</v>
+        <v>0.5243</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7829</v>
+        <v>0.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3099</v>
+        <v>0.1243</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7929</v>
+        <v>-0.3429</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0505</v>
+        <v>-0.5191</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8434</v>
+        <v>0.1762</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6455</v>
+        <v>-0.6199</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0806</v>
+        <v>-0.66</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5648</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1474</v>
+        <v>0.277</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1312</v>
+        <v>0.1409</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2786</v>
+        <v>0.136</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1309</v>
+        <v>0.6688</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4364</v>
+        <v>0.7539</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5673</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4774</v>
+        <v>-0.637</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9077</v>
+        <v>-1.1514</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4303</v>
+        <v>0.5144</v>
       </c>
       <c r="G8" t="n">
         <v>1.1215</v>
@@ -1078,13 +1078,13 @@
         <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0675</v>
+        <v>-0.0921</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3798</v>
+        <v>0.1361</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3124</v>
+        <v>-0.2282</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6745</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5691</v>
+        <v>-2.4953</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.74</v>
+        <v>-2.1051</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1709</v>
+        <v>-0.3902</v>
       </c>
       <c r="G9" t="n">
         <v>0.0774</v>
@@ -1156,13 +1156,13 @@
         <v>2.1822</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.5216</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2242</v>
+        <v>-0.5894</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6289</v>
+        <v>0.0678</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2495</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0362</v>
+        <v>-3.4294</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3005</v>
+        <v>-3.6657</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2643</v>
+        <v>0.2362</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1508</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3904</v>
+        <v>-0.7837</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0485</v>
+        <v>-0.4137</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3419</v>
+        <v>-0.37</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5111</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9986</v>
+        <v>-6.0562</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4237</v>
+        <v>-3.5654</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.575</v>
+        <v>-2.4908</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3301</v>
@@ -1312,13 +1312,13 @@
         <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1412</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3175</v>
+        <v>0.1758</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1763</v>
+        <v>-0.0922</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4129</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.277000000000001</v>
+        <v>-2.653500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.390600000000001</v>
+        <v>-5.766900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1134</v>
+        <v>3.113300000000001</v>
       </c>
       <c r="G12" t="n">
         <v>8.4903</v>
@@ -1390,10 +1390,10 @@
         <v>11.9032</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.259300000000001</v>
+        <v>-2.6362</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6793999999999999</v>
+        <v>-0.05600000000000005</v>
       </c>
       <c r="U12" t="n">
         <v>-2.5801</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.1113</v>
+        <v>9.8673</v>
       </c>
       <c r="E13" t="n">
-        <v>8.8325</v>
+        <v>8.4244</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2788</v>
+        <v>1.4429</v>
       </c>
       <c r="G13" t="n">
         <v>8.789300000000001</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2544</v>
+        <v>1.0104</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9921</v>
+        <v>0.5839</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2623</v>
+        <v>0.4264</v>
       </c>
       <c r="V13" t="n">
         <v>0.266</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4712</v>
+        <v>3.9126</v>
       </c>
       <c r="E14" t="n">
-        <v>3.556</v>
+        <v>2.8418</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9152</v>
+        <v>1.0708</v>
       </c>
       <c r="G14" t="n">
         <v>1.8399</v>
@@ -1546,13 +1546,13 @@
         <v>2.1822</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0479</v>
+        <v>1.4894</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8196</v>
+        <v>1.1054</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2283</v>
+        <v>0.3839</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4085</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9501</v>
+        <v>2.6583</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4244</v>
+        <v>1.8325</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.8258</v>
       </c>
       <c r="G15" t="n">
         <v>1.4496</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6898</v>
+        <v>0.0185</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4761</v>
+        <v>-0.0679</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2137</v>
+        <v>0.0864</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0617</v>
+        <v>0.8959</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0318</v>
+        <v>-0.3379</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0936</v>
+        <v>1.2339</v>
       </c>
       <c r="G16" t="n">
         <v>0.067</v>
@@ -1702,13 +1702,13 @@
         <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2013</v>
+        <v>0.0354</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1814</v>
+        <v>-0.1247</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0198</v>
+        <v>0.1601</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8708</v>
+        <v>0.4627</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8708</v>
+        <v>0.4627</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6802</v>
+        <v>0.2721</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6802</v>
+        <v>0.2721</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1799,11 +1799,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>J. ARNAL DIAZ</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1813,71 +1809,75 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4699</v>
+        <v>-0.2975</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3688</v>
+        <v>0.3628</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1011</v>
+        <v>-0.6602</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1914</v>
+        <v>-1.0712</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4635</v>
+        <v>-1.2604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2721</v>
+        <v>0.1892</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0053</v>
+        <v>0.1813</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0053</v>
+        <v>0.1411</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1967</v>
+        <v>-1.2525</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4688</v>
+        <v>-1.4015</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2721</v>
+        <v>0.149</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5827</v>
+        <v>-0.2182</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6178</v>
+        <v>0.1815</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0352</v>
+        <v>-0.3996</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>. VICENTE SABARIEGO</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6561</v>
+        <v>-0.2975</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5555</v>
+        <v>0.3628</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1006</v>
+        <v>-0.6602</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0712</v>
@@ -1932,13 +1932,13 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5768</v>
+        <v>-0.2182</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7368</v>
+        <v>0.1815</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8401</v>
+        <v>-0.3996</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6561</v>
+        <v>-0.7521</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5555</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1006</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0712</v>
+        <v>-0.1914</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2604</v>
+        <v>-0.4635</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1892</v>
+        <v>0.2721</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1813</v>
+        <v>0.0053</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1411</v>
+        <v>0.0053</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2525</v>
+        <v>-0.1967</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4015</v>
+        <v>-0.4688</v>
       </c>
       <c r="O20" t="n">
-        <v>0.149</v>
+        <v>0.2721</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9919</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5768</v>
+        <v>0.3004</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7368</v>
+        <v>0.3118</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8401</v>
+        <v>-0.0113</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="21">
@@ -2043,13 +2043,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7677</v>
+        <v>-1.1053</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2888</v>
+        <v>-2.9827</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5211</v>
+        <v>1.8773</v>
       </c>
       <c r="G21" t="n">
         <v>-5.1319</v>
@@ -2088,13 +2088,13 @@
         <v>2.3806</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6853</v>
+        <v>1.3476</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5216</v>
+        <v>0.8277</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1637</v>
+        <v>0.5199</v>
       </c>
       <c r="V21" t="n">
         <v>2.6789</v>
@@ -2109,7 +2109,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,73 +2121,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7939</v>
+        <v>-2.212</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9811</v>
+        <v>-3.6841</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1873</v>
+        <v>1.4721</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6904</v>
+        <v>-3.4336</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4691</v>
+        <v>-2.9984</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7786</v>
+        <v>-0.4353</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3577</v>
+        <v>-2.8088</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0003</v>
+        <v>-2.2114</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6425999999999999</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3328</v>
+        <v>-0.6249</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4688</v>
+        <v>-0.7869</v>
       </c>
       <c r="O22" t="n">
-        <v>0.136</v>
+        <v>0.162</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3968</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>-3.3725</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5952</v>
+        <v>2.7774</v>
       </c>
       <c r="S22" t="n">
-        <v>0.488</v>
+        <v>0.3444</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3685</v>
+        <v>-0.4477</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1196</v>
+        <v>0.792</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1947</v>
+        <v>1.4724</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.9449</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1947</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,67 +2199,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0307</v>
+        <v>-2.2862</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8445</v>
+        <v>-2.3892</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8138</v>
+        <v>0.1031</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.4999</v>
+        <v>-1.6904</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.0697</v>
+        <v>-2.4691</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4302</v>
+        <v>0.7786</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.5948</v>
+        <v>-1.3577</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.8796</v>
+        <v>-2.0003</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7153</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9051</v>
+        <v>-0.3328</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1902</v>
+        <v>-0.4688</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2851</v>
+        <v>0.136</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5871</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6161</v>
+        <v>-0.0042</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3173</v>
+        <v>-0.0396</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9334</v>
+        <v>0.0354</v>
       </c>
       <c r="V23" t="n">
-        <v>0.266</v>
+        <v>-0.1947</v>
       </c>
       <c r="W23" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
     </row>
     <row r="24">
@@ -2277,13 +2277,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1875</v>
+        <v>-2.793</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3283</v>
+        <v>-2.4303</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8591</v>
+        <v>-0.3626</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5421</v>
@@ -2322,13 +2322,13 @@
         <v>1.3887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3037</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.0112</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3945</v>
+        <v>0.102</v>
       </c>
       <c r="V24" t="n">
         <v>-0.532</v>
@@ -2343,7 +2343,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E. MAÑES CARRETERO</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2355,67 +2355,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.2824</v>
+        <v>-2.9312</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3983</v>
+        <v>-4.4364</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1158</v>
+        <v>1.5052</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.4336</v>
+        <v>-5.4999</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.9984</v>
+        <v>-5.0697</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4353</v>
+        <v>-0.4302</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.8088</v>
+        <v>-4.5948</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2114</v>
+        <v>-3.8796</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.7153</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6249</v>
+        <v>-0.9051</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7869</v>
+        <v>-1.1902</v>
       </c>
       <c r="O25" t="n">
-        <v>0.162</v>
+        <v>0.2851</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.3725</v>
+        <v>-0.1984</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7774</v>
+        <v>1.7855</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7261</v>
+        <v>0.7156</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1619</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4358</v>
+        <v>0.6248</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4724</v>
+        <v>0.266</v>
       </c>
       <c r="W25" t="n">
-        <v>2.9449</v>
+        <v>0.266</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2433,16 +2433,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.6208</v>
+        <v>5.122</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.668899999999999</v>
+        <v>-2.648499999999997</v>
       </c>
       <c r="F26" t="n">
-        <v>5.2899</v>
+        <v>7.7708</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.561199999999999</v>
+        <v>-9.561199999999998</v>
       </c>
       <c r="H26" t="n">
         <v>-7.709900000000001</v>
@@ -2451,16 +2451,16 @@
         <v>-1.8515</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2255000000000007</v>
+        <v>-0.2255000000000003</v>
       </c>
       <c r="K26" t="n">
-        <v>3.297799999999997</v>
+        <v>3.297799999999999</v>
       </c>
       <c r="L26" t="n">
         <v>-3.5233</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.336</v>
+        <v>-9.336000000000002</v>
       </c>
       <c r="N26" t="n">
         <v>-11.0078</v>
@@ -2469,7 +2469,7 @@
         <v>1.6718</v>
       </c>
       <c r="P26" t="n">
-        <v>5.951299999999999</v>
+        <v>5.9513</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.903</v>
@@ -2478,13 +2478,13 @@
         <v>17.8546</v>
       </c>
       <c r="S26" t="n">
-        <v>1.6827</v>
+        <v>5.184</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8431</v>
+        <v>2.8636</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1607</v>
+        <v>2.3204</v>
       </c>
       <c r="V26" t="n">
         <v>3.5481</v>
